--- a/data/dividends_info_20261008.xlsx
+++ b/data/dividends_info_20261008.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>48.20500183105469</v>
+        <v>47.98500061035156</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1867026171172554</v>
+        <v>0.1875586096805941</v>
       </c>
       <c r="J2" t="n">
         <v>158</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>61.09999847412109</v>
+        <v>60.09999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.145662876401683</v>
+        <v>1.164725487141931</v>
       </c>
       <c r="J3" t="n">
         <v>137</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.720000267028809</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6880733734248379</v>
+        <v>0.674157332266361</v>
       </c>
       <c r="J4" t="n">
         <v>67</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>48.18999862670898</v>
+        <v>47.98500061035156</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1867607440646784</v>
+        <v>0.1875586096805941</v>
       </c>
       <c r="J6" t="n">
         <v>67</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.059999942779541</v>
+        <v>2.065000057220459</v>
       </c>
       <c r="I7" t="n">
-        <v>3.737864181496264</v>
+        <v>3.728813455997861</v>
       </c>
       <c r="J7" t="n">
         <v>46</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>47.7599983215332</v>
+        <v>47.65999984741211</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6490787497792532</v>
+        <v>0.6504406231483291</v>
       </c>
       <c r="J8" t="n">
         <v>46</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>24.84499931335449</v>
+        <v>24.8799991607666</v>
       </c>
       <c r="I9" t="n">
-        <v>1.086737804234399</v>
+        <v>1.085209039820887</v>
       </c>
       <c r="J9" t="n">
         <v>46</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>25.26000022888184</v>
+        <v>25.25</v>
       </c>
       <c r="I10" t="n">
-        <v>2.335708609081502</v>
+        <v>2.336633663366336</v>
       </c>
       <c r="J10" t="n">
         <v>46</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>11.39999961853027</v>
+        <v>11.26000022888184</v>
       </c>
       <c r="I11" t="n">
-        <v>1.842105324798896</v>
+        <v>1.865008843084667</v>
       </c>
       <c r="J11" t="n">
         <v>39</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.980000019073486</v>
+        <v>5.96999979019165</v>
       </c>
       <c r="I12" t="n">
-        <v>3.344481594683792</v>
+        <v>3.350083869828403</v>
       </c>
       <c r="J12" t="n">
         <v>39</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>8.020000457763672</v>
+        <v>8.010000228881836</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7481296331089067</v>
+        <v>0.7490636490078573</v>
       </c>
       <c r="J14" t="n">
         <v>32</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>10.69999980926514</v>
+        <v>10.63000011444092</v>
       </c>
       <c r="I15" t="n">
-        <v>4.299065497194548</v>
+        <v>4.327375306187318</v>
       </c>
       <c r="J15" t="n">
         <v>18</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>7.440000057220459</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="I19" t="n">
-        <v>0.510752684243884</v>
+        <v>0.5135135068956129</v>
       </c>
       <c r="J19" t="n">
         <v>-10</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>24.84499931335449</v>
+        <v>24.8799991607666</v>
       </c>
       <c r="I20" t="n">
-        <v>1.086737804234399</v>
+        <v>1.085209039820887</v>
       </c>
       <c r="J20" t="n">
         <v>-17</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.919999957084656</v>
+        <v>1.89900004863739</v>
       </c>
       <c r="I21" t="n">
-        <v>2.968750066356735</v>
+        <v>3.001579701954185</v>
       </c>
       <c r="J21" t="n">
         <v>-17</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>48.18999862670898</v>
+        <v>47.98500061035156</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1867607440646784</v>
+        <v>0.1875586096805941</v>
       </c>
       <c r="J22" t="n">
         <v>-17</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>93.55000305175781</v>
+        <v>93.5</v>
       </c>
       <c r="I23" t="n">
-        <v>1.421699579490296</v>
+        <v>1.422459893048128</v>
       </c>
       <c r="J23" t="n">
         <v>-17</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5.920000076293945</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="I24" t="n">
-        <v>5.067567502259338</v>
+        <v>5.08474568052218</v>
       </c>
       <c r="J24" t="n">
         <v>-24</v>
@@ -3371,7 +3371,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3388,7 +3388,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3466,14 +3466,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3490,7 +3490,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3507,7 +3507,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3517,14 +3517,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3568,14 +3568,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3585,14 +3585,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3602,14 +3602,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3626,7 +3626,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3643,7 +3643,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3653,14 +3653,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3677,7 +3677,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3694,7 +3694,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3704,14 +3704,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3728,7 +3728,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3738,14 +3738,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3762,7 +3762,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3789,14 +3789,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3813,7 +3813,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3840,14 +3840,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3857,14 +3857,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3881,7 +3881,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3898,7 +3898,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3915,7 +3915,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3932,7 +3932,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3949,7 +3949,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3966,7 +3966,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3983,7 +3983,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4000,7 +4000,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4010,14 +4010,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4034,7 +4034,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4051,7 +4051,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4068,7 +4068,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4085,7 +4085,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4095,14 +4095,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4119,7 +4119,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4146,14 +4146,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4170,7 +4170,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4187,7 +4187,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -4214,14 +4214,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4231,14 +4231,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4276,61 +4276,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>